--- a/data/trans_orig/P20D2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -991,62 +991,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -1299,97 +1299,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>361</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>324</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>475</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44107</t>
+          <t>44686</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Edad-trans_orig.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>947</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1477,27 +1477,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>468</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17724</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>724</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>949</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>380</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,22 +3188,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>492</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>72878</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
